--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N2_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N2_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.81355923089742</v>
+        <v>5.332203375020831</v>
       </c>
       <c r="D2" t="n">
-        <v>31.17169619902712</v>
+        <v>5.065400632341908</v>
       </c>
       <c r="E2" t="n">
-        <v>10.04844072221613</v>
+        <v>1.632871617360122</v>
       </c>
       <c r="F2" t="n">
-        <v>9.108143956927719</v>
+        <v>1.480073393000754</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.35313203801003</v>
+        <v>5.09488395617663</v>
       </c>
       <c r="D3" t="n">
-        <v>7.494100476382309</v>
+        <v>1.217791327412125</v>
       </c>
       <c r="E3" t="n">
-        <v>10.04844072221613</v>
+        <v>1.632871617360122</v>
       </c>
       <c r="F3" t="n">
-        <v>9.108143956927719</v>
+        <v>1.480073393000754</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.67742998019622</v>
+        <v>2.060082371781886</v>
       </c>
       <c r="D4" t="n">
-        <v>25.03970479127383</v>
+        <v>4.068952028581998</v>
       </c>
       <c r="E4" t="n">
-        <v>10.04844072221613</v>
+        <v>1.632871617360122</v>
       </c>
       <c r="F4" t="n">
-        <v>9.108143956927719</v>
+        <v>1.480073393000754</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>9.116663284055287</v>
+        <v>1.481457783658984</v>
       </c>
       <c r="D5" t="n">
-        <v>10.08322583454478</v>
+        <v>1.638524198113527</v>
       </c>
       <c r="E5" t="n">
-        <v>10.04844072221613</v>
+        <v>1.632871617360122</v>
       </c>
       <c r="F5" t="n">
-        <v>9.108143956927719</v>
+        <v>1.480073393000754</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.69672243743542</v>
+        <v>2.225717396083255</v>
       </c>
       <c r="D6" t="n">
-        <v>13.51120981550802</v>
+        <v>2.195571595020054</v>
       </c>
       <c r="E6" t="n">
-        <v>10.04844072221613</v>
+        <v>1.632871617360122</v>
       </c>
       <c r="F6" t="n">
-        <v>9.108143956927719</v>
+        <v>1.480073393000754</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
